--- a/templates/cagi/양식_청소년도박문제선별검사_CAGI_3.xlsx
+++ b/templates/cagi/양식_청소년도박문제선별검사_CAGI_3.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\night\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHASE\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B519B83-DFBF-4382-A025-086275267EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="청소년도박문제선별검사" sheetId="1" r:id="rId1"/>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>청소년 도박문제 선별검사(CAGI) 일괄 등록 양식 (3행 부터 입력해 주세요)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -410,20 +409,11 @@
     <t>학교외기관</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>중학교</t>
-  </si>
-  <si>
-    <t>2학년</t>
-  </si>
-  <si>
-    <t>여</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
@@ -1001,8 +991,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.375" style="10" customWidth="1"/>
@@ -1071,47 +1061,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
@@ -1121,31 +1070,31 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>코드!$A$2:$A$21</xm:f>
           </x14:formula1>
           <xm:sqref>A3:A1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>코드!$B$2:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>코드!$C$2:$C$5</xm:f>
           </x14:formula1>
           <xm:sqref>C3:C1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>코드!$D$2:$D$8</xm:f>
           </x14:formula1>
           <xm:sqref>D3:D1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>코드!$E$2:$E$5</xm:f>
           </x14:formula1>
@@ -1158,7 +1107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1169,7 +1118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
